--- a/lang/ar/headTags.xlsx
+++ b/lang/ar/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1189</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2355">
   <si>
     <t>en</t>
   </si>
@@ -6571,439 +6571,442 @@
     <t>أرض العجائب الملتوية</t>
   </si>
   <si>
+    <t>ULTRAKILL</t>
+  </si>
+  <si>
+    <t>Umineko - When They Cry</t>
+  </si>
+  <si>
+    <t>أومينيكو - عندما يبكون</t>
+  </si>
+  <si>
+    <t>Undertale</t>
+  </si>
+  <si>
+    <t>أندرتيل</t>
+  </si>
+  <si>
+    <t>Undertale AU</t>
+  </si>
+  <si>
+    <t>أندرتيل AU</t>
+  </si>
+  <si>
+    <t>Undertale Yellow</t>
+  </si>
+  <si>
+    <t>Universal Symbol</t>
+  </si>
+  <si>
+    <t>الرمز العالمي</t>
+  </si>
+  <si>
+    <t>Up</t>
+  </si>
+  <si>
+    <t>فوق</t>
+  </si>
+  <si>
+    <t>Urban Wildlife</t>
+  </si>
+  <si>
+    <t>الحياة البرية الحضرية</t>
+  </si>
+  <si>
+    <t>V for Vendetta</t>
+  </si>
+  <si>
+    <t>Valentines</t>
+  </si>
+  <si>
+    <t>فالنتاينز</t>
+  </si>
+  <si>
+    <t>Valorant</t>
+  </si>
+  <si>
+    <t>فالورانت</t>
+  </si>
+  <si>
+    <t>Vanilla (removed)</t>
+  </si>
+  <si>
+    <t>فانيلا (تمت إزالته)</t>
+  </si>
+  <si>
+    <t>Vanilla Block</t>
+  </si>
+  <si>
+    <t>كتلة الفانيليا</t>
+  </si>
+  <si>
+    <t>Vanilla Food</t>
+  </si>
+  <si>
+    <t>طعام الفانيليا</t>
+  </si>
+  <si>
+    <t>Vanilla Helmet</t>
+  </si>
+  <si>
+    <t>خوذة الفانيليا</t>
+  </si>
+  <si>
+    <t>Vanilla Item</t>
+  </si>
+  <si>
+    <t>عنصر فانيلا</t>
+  </si>
+  <si>
+    <t>Vanilla Mob</t>
+  </si>
+  <si>
+    <t>غوغاء الفانيليا</t>
+  </si>
+  <si>
+    <t>Vault Hunters</t>
+  </si>
+  <si>
+    <t>صيادو القبو</t>
+  </si>
+  <si>
+    <t>Vegetable</t>
+  </si>
+  <si>
+    <t>خضروات</t>
+  </si>
+  <si>
+    <t>Vehicle</t>
+  </si>
+  <si>
+    <t>مركبة</t>
+  </si>
+  <si>
+    <t>Vikings</t>
+  </si>
+  <si>
+    <t>الفايكنج</t>
+  </si>
+  <si>
+    <t>Villager</t>
+  </si>
+  <si>
+    <t>قروي</t>
+  </si>
+  <si>
+    <t>Villager (Desert)</t>
+  </si>
+  <si>
+    <t>قروي (صحراوي)</t>
+  </si>
+  <si>
+    <t>Villager (Jungle)</t>
+  </si>
+  <si>
+    <t>قروي (الغابة)</t>
+  </si>
+  <si>
+    <t>Villager (Plains)</t>
+  </si>
+  <si>
+    <t>قروي (السهول)</t>
+  </si>
+  <si>
+    <t>Villager (Savanna)</t>
+  </si>
+  <si>
+    <t>قروي (سافانا)</t>
+  </si>
+  <si>
+    <t>Villager (Snowy Tundra)</t>
+  </si>
+  <si>
+    <t>قروي (التندرا الثلجية)</t>
+  </si>
+  <si>
+    <t>Villager (Swamp)</t>
+  </si>
+  <si>
+    <t>قروي (مستنقع)</t>
+  </si>
+  <si>
+    <t>Villager (Taiga)</t>
+  </si>
+  <si>
+    <t>قروي (تايغا)</t>
+  </si>
+  <si>
+    <t>Virtual Youtuber</t>
+  </si>
+  <si>
+    <t>قروي افتراضي</t>
+  </si>
+  <si>
+    <t>Vocaloid</t>
+  </si>
+  <si>
+    <t>فوكالويد</t>
+  </si>
+  <si>
+    <t>Voltron</t>
+  </si>
+  <si>
+    <t>فولترون</t>
+  </si>
+  <si>
+    <t>Wakfu</t>
+  </si>
+  <si>
+    <t>واكفو</t>
+  </si>
+  <si>
+    <t>Walking Dead</t>
+  </si>
+  <si>
+    <t>الموتى السائرون</t>
+  </si>
+  <si>
+    <t>Wall-E</t>
+  </si>
+  <si>
+    <t>وال-إي</t>
+  </si>
+  <si>
+    <t>Wallace and Gromit</t>
+  </si>
+  <si>
+    <t>والاس وجروميت</t>
+  </si>
+  <si>
+    <t>War of the Worlds</t>
+  </si>
+  <si>
+    <t>حرب العوالم</t>
+  </si>
+  <si>
+    <t>Warcraft</t>
+  </si>
+  <si>
+    <t>واركرافت</t>
+  </si>
+  <si>
+    <t>Warframe</t>
+  </si>
+  <si>
+    <t>وارفريم</t>
+  </si>
+  <si>
+    <t>Warhammer</t>
+  </si>
+  <si>
+    <t>Warrior Cats</t>
+  </si>
+  <si>
+    <t>القطط المحاربة</t>
+  </si>
+  <si>
+    <t>We Bear Bears</t>
+  </si>
+  <si>
+    <t>نحن دببة الدببة</t>
+  </si>
+  <si>
+    <t>We Happy Few</t>
+  </si>
+  <si>
+    <t>نحن القلة السعداء</t>
+  </si>
+  <si>
+    <t>Weather</t>
+  </si>
+  <si>
+    <t>الطقس</t>
+  </si>
+  <si>
+    <t>Welcome Home</t>
+  </si>
+  <si>
+    <t>مرحبًا بك في بيتك</t>
+  </si>
+  <si>
+    <t>Who is this?</t>
+  </si>
+  <si>
+    <t>من هذا؟</t>
+  </si>
+  <si>
+    <t>Wild Update</t>
+  </si>
+  <si>
+    <t>تحديث البرية</t>
+  </si>
+  <si>
+    <t>Wings of Fire</t>
+  </si>
+  <si>
+    <t>أجنحة النار</t>
+  </si>
+  <si>
+    <t>Winnie the Pooh</t>
+  </si>
+  <si>
+    <t>ويني ذا بوو</t>
+  </si>
+  <si>
+    <t>Winter</t>
+  </si>
+  <si>
+    <t>وينتر</t>
+  </si>
+  <si>
+    <t>Witcher</t>
+  </si>
+  <si>
+    <t>ويتشر</t>
+  </si>
+  <si>
+    <t>Wonderful Wonder World</t>
+  </si>
+  <si>
+    <t>عالم العجائب الرائع</t>
+  </si>
+  <si>
+    <t>Wood</t>
+  </si>
+  <si>
+    <t>خشب</t>
+  </si>
+  <si>
+    <t>Wool</t>
+  </si>
+  <si>
+    <t>صوف</t>
+  </si>
+  <si>
+    <t>Work Safety Helmet</t>
+  </si>
+  <si>
+    <t>خوذة سلامة العمل</t>
+  </si>
+  <si>
+    <t>Wreck It Ralph</t>
+  </si>
+  <si>
+    <t>وريك إت رالف</t>
+  </si>
+  <si>
+    <t>Wybel</t>
+  </si>
+  <si>
+    <t>ويبل</t>
+  </si>
+  <si>
+    <t>Wynncraft</t>
+  </si>
+  <si>
+    <t>وينكرافت</t>
+  </si>
+  <si>
+    <t>X-Men</t>
+  </si>
+  <si>
+    <t>إكس-مين</t>
+  </si>
+  <si>
+    <t>Xenoblade Chronicles</t>
+  </si>
+  <si>
+    <t>زينوبليد كرونيكلز</t>
+  </si>
+  <si>
+    <t>Yandere Simulator</t>
+  </si>
+  <si>
+    <t>محاكي ياندير</t>
+  </si>
+  <si>
+    <t>Yellow Submarine</t>
+  </si>
+  <si>
+    <t>الغواصة الصفراء</t>
+  </si>
+  <si>
+    <t>Yokai</t>
+  </si>
+  <si>
+    <t>يوكاي</t>
+  </si>
+  <si>
+    <t>Yooka Laylee</t>
+  </si>
+  <si>
+    <t>يوكا ليلي</t>
+  </si>
+  <si>
+    <t>Young</t>
+  </si>
+  <si>
+    <t>يونغ</t>
+  </si>
+  <si>
+    <t>Youtube</t>
+  </si>
+  <si>
+    <t>يوتيوب</t>
+  </si>
+  <si>
+    <t>Yu-Gi-Oh</t>
+  </si>
+  <si>
+    <t>يو-جي-أوه</t>
+  </si>
+  <si>
+    <t>Yume Nikki</t>
+  </si>
+  <si>
+    <t>يومي نيكي</t>
+  </si>
+  <si>
+    <t>Zero no Tsukaima</t>
+  </si>
+  <si>
+    <t>زيرو نو تسوكايما</t>
+  </si>
+  <si>
+    <t>Zero Wing</t>
+  </si>
+  <si>
+    <t>زيرو وينج</t>
+  </si>
+  <si>
+    <t>Zodiac Sign</t>
+  </si>
+  <si>
+    <t>علامة زودياك</t>
+  </si>
+  <si>
+    <t>Zombie</t>
+  </si>
+  <si>
+    <t>زومبي</t>
+  </si>
+  <si>
+    <t>Zombie (Vanilla)</t>
+  </si>
+  <si>
+    <t>زومبي (فانيليا)</t>
+  </si>
+  <si>
+    <t>Zootopia</t>
+  </si>
+  <si>
+    <t>زوتوبيا</t>
+  </si>
+  <si>
     <t>Ultrakill</t>
   </si>
   <si>
     <t>ألترا كيل</t>
-  </si>
-  <si>
-    <t>Umineko - When They Cry</t>
-  </si>
-  <si>
-    <t>أومينيكو - عندما يبكون</t>
-  </si>
-  <si>
-    <t>Undertale</t>
-  </si>
-  <si>
-    <t>أندرتيل</t>
-  </si>
-  <si>
-    <t>Undertale AU</t>
-  </si>
-  <si>
-    <t>أندرتيل AU</t>
-  </si>
-  <si>
-    <t>Undertale Yellow</t>
-  </si>
-  <si>
-    <t>Universal Symbol</t>
-  </si>
-  <si>
-    <t>الرمز العالمي</t>
-  </si>
-  <si>
-    <t>Up</t>
-  </si>
-  <si>
-    <t>فوق</t>
-  </si>
-  <si>
-    <t>Urban Wildlife</t>
-  </si>
-  <si>
-    <t>الحياة البرية الحضرية</t>
-  </si>
-  <si>
-    <t>V for Vendetta</t>
-  </si>
-  <si>
-    <t>Valentines</t>
-  </si>
-  <si>
-    <t>فالنتاينز</t>
-  </si>
-  <si>
-    <t>Valorant</t>
-  </si>
-  <si>
-    <t>فالورانت</t>
-  </si>
-  <si>
-    <t>Vanilla (removed)</t>
-  </si>
-  <si>
-    <t>فانيلا (تمت إزالته)</t>
-  </si>
-  <si>
-    <t>Vanilla Block</t>
-  </si>
-  <si>
-    <t>كتلة الفانيليا</t>
-  </si>
-  <si>
-    <t>Vanilla Food</t>
-  </si>
-  <si>
-    <t>طعام الفانيليا</t>
-  </si>
-  <si>
-    <t>Vanilla Helmet</t>
-  </si>
-  <si>
-    <t>خوذة الفانيليا</t>
-  </si>
-  <si>
-    <t>Vanilla Item</t>
-  </si>
-  <si>
-    <t>عنصر فانيلا</t>
-  </si>
-  <si>
-    <t>Vanilla Mob</t>
-  </si>
-  <si>
-    <t>غوغاء الفانيليا</t>
-  </si>
-  <si>
-    <t>Vault Hunters</t>
-  </si>
-  <si>
-    <t>صيادو القبو</t>
-  </si>
-  <si>
-    <t>Vegetable</t>
-  </si>
-  <si>
-    <t>خضروات</t>
-  </si>
-  <si>
-    <t>Vehicle</t>
-  </si>
-  <si>
-    <t>مركبة</t>
-  </si>
-  <si>
-    <t>Vikings</t>
-  </si>
-  <si>
-    <t>الفايكنج</t>
-  </si>
-  <si>
-    <t>Villager</t>
-  </si>
-  <si>
-    <t>قروي</t>
-  </si>
-  <si>
-    <t>Villager (Desert)</t>
-  </si>
-  <si>
-    <t>قروي (صحراوي)</t>
-  </si>
-  <si>
-    <t>Villager (Jungle)</t>
-  </si>
-  <si>
-    <t>قروي (الغابة)</t>
-  </si>
-  <si>
-    <t>Villager (Plains)</t>
-  </si>
-  <si>
-    <t>قروي (السهول)</t>
-  </si>
-  <si>
-    <t>Villager (Savanna)</t>
-  </si>
-  <si>
-    <t>قروي (سافانا)</t>
-  </si>
-  <si>
-    <t>Villager (Snowy Tundra)</t>
-  </si>
-  <si>
-    <t>قروي (التندرا الثلجية)</t>
-  </si>
-  <si>
-    <t>Villager (Swamp)</t>
-  </si>
-  <si>
-    <t>قروي (مستنقع)</t>
-  </si>
-  <si>
-    <t>Villager (Taiga)</t>
-  </si>
-  <si>
-    <t>قروي (تايغا)</t>
-  </si>
-  <si>
-    <t>Virtual Youtuber</t>
-  </si>
-  <si>
-    <t>قروي افتراضي</t>
-  </si>
-  <si>
-    <t>Vocaloid</t>
-  </si>
-  <si>
-    <t>فوكالويد</t>
-  </si>
-  <si>
-    <t>Voltron</t>
-  </si>
-  <si>
-    <t>فولترون</t>
-  </si>
-  <si>
-    <t>Wakfu</t>
-  </si>
-  <si>
-    <t>واكفو</t>
-  </si>
-  <si>
-    <t>Walking Dead</t>
-  </si>
-  <si>
-    <t>الموتى السائرون</t>
-  </si>
-  <si>
-    <t>Wall-E</t>
-  </si>
-  <si>
-    <t>وال-إي</t>
-  </si>
-  <si>
-    <t>Wallace and Gromit</t>
-  </si>
-  <si>
-    <t>والاس وجروميت</t>
-  </si>
-  <si>
-    <t>War of the Worlds</t>
-  </si>
-  <si>
-    <t>حرب العوالم</t>
-  </si>
-  <si>
-    <t>Warcraft</t>
-  </si>
-  <si>
-    <t>واركرافت</t>
-  </si>
-  <si>
-    <t>Warframe</t>
-  </si>
-  <si>
-    <t>وارفريم</t>
-  </si>
-  <si>
-    <t>Warhammer</t>
-  </si>
-  <si>
-    <t>Warrior Cats</t>
-  </si>
-  <si>
-    <t>القطط المحاربة</t>
-  </si>
-  <si>
-    <t>We Bear Bears</t>
-  </si>
-  <si>
-    <t>نحن دببة الدببة</t>
-  </si>
-  <si>
-    <t>We Happy Few</t>
-  </si>
-  <si>
-    <t>نحن القلة السعداء</t>
-  </si>
-  <si>
-    <t>Weather</t>
-  </si>
-  <si>
-    <t>الطقس</t>
-  </si>
-  <si>
-    <t>Welcome Home</t>
-  </si>
-  <si>
-    <t>مرحبًا بك في بيتك</t>
-  </si>
-  <si>
-    <t>Who is this?</t>
-  </si>
-  <si>
-    <t>من هذا؟</t>
-  </si>
-  <si>
-    <t>Wild Update</t>
-  </si>
-  <si>
-    <t>تحديث البرية</t>
-  </si>
-  <si>
-    <t>Wings of Fire</t>
-  </si>
-  <si>
-    <t>أجنحة النار</t>
-  </si>
-  <si>
-    <t>Winnie the Pooh</t>
-  </si>
-  <si>
-    <t>ويني ذا بوو</t>
-  </si>
-  <si>
-    <t>Winter</t>
-  </si>
-  <si>
-    <t>وينتر</t>
-  </si>
-  <si>
-    <t>Witcher</t>
-  </si>
-  <si>
-    <t>ويتشر</t>
-  </si>
-  <si>
-    <t>Wonderful Wonder World</t>
-  </si>
-  <si>
-    <t>عالم العجائب الرائع</t>
-  </si>
-  <si>
-    <t>Wood</t>
-  </si>
-  <si>
-    <t>خشب</t>
-  </si>
-  <si>
-    <t>Wool</t>
-  </si>
-  <si>
-    <t>صوف</t>
-  </si>
-  <si>
-    <t>Work Safety Helmet</t>
-  </si>
-  <si>
-    <t>خوذة سلامة العمل</t>
-  </si>
-  <si>
-    <t>Wreck It Ralph</t>
-  </si>
-  <si>
-    <t>وريك إت رالف</t>
-  </si>
-  <si>
-    <t>Wybel</t>
-  </si>
-  <si>
-    <t>ويبل</t>
-  </si>
-  <si>
-    <t>Wynncraft</t>
-  </si>
-  <si>
-    <t>وينكرافت</t>
-  </si>
-  <si>
-    <t>X-Men</t>
-  </si>
-  <si>
-    <t>إكس-مين</t>
-  </si>
-  <si>
-    <t>Xenoblade Chronicles</t>
-  </si>
-  <si>
-    <t>زينوبليد كرونيكلز</t>
-  </si>
-  <si>
-    <t>Yandere Simulator</t>
-  </si>
-  <si>
-    <t>محاكي ياندير</t>
-  </si>
-  <si>
-    <t>Yellow Submarine</t>
-  </si>
-  <si>
-    <t>الغواصة الصفراء</t>
-  </si>
-  <si>
-    <t>Yokai</t>
-  </si>
-  <si>
-    <t>يوكاي</t>
-  </si>
-  <si>
-    <t>Yooka Laylee</t>
-  </si>
-  <si>
-    <t>يوكا ليلي</t>
-  </si>
-  <si>
-    <t>Young</t>
-  </si>
-  <si>
-    <t>يونغ</t>
-  </si>
-  <si>
-    <t>Youtube</t>
-  </si>
-  <si>
-    <t>يوتيوب</t>
-  </si>
-  <si>
-    <t>Yu-Gi-Oh</t>
-  </si>
-  <si>
-    <t>يو-جي-أوه</t>
-  </si>
-  <si>
-    <t>Yume Nikki</t>
-  </si>
-  <si>
-    <t>يومي نيكي</t>
-  </si>
-  <si>
-    <t>Zero no Tsukaima</t>
-  </si>
-  <si>
-    <t>زيرو نو تسوكايما</t>
-  </si>
-  <si>
-    <t>Zero Wing</t>
-  </si>
-  <si>
-    <t>زيرو وينج</t>
-  </si>
-  <si>
-    <t>Zodiac Sign</t>
-  </si>
-  <si>
-    <t>علامة زودياك</t>
-  </si>
-  <si>
-    <t>Zombie</t>
-  </si>
-  <si>
-    <t>زومبي</t>
-  </si>
-  <si>
-    <t>Zombie (Vanilla)</t>
-  </si>
-  <si>
-    <t>زومبي (فانيليا)</t>
-  </si>
-  <si>
-    <t>Zootopia</t>
-  </si>
-  <si>
-    <t>زوتوبيا</t>
   </si>
   <si>
     <t>Hypixel (Mutations) Tag</t>
@@ -7425,7 +7428,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1188"/>
+  <dimension ref="A1:B1189"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -16245,631 +16248,631 @@
         <v>2184</v>
       </c>
       <c r="B1102" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
+        <v>2185</v>
+      </c>
+      <c r="B1103" t="s">
         <v>2186</v>
-      </c>
-      <c r="B1103" t="s">
-        <v>2187</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
+        <v>2187</v>
+      </c>
+      <c r="B1104" t="s">
         <v>2188</v>
-      </c>
-      <c r="B1104" t="s">
-        <v>2189</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
+        <v>2189</v>
+      </c>
+      <c r="B1105" t="s">
         <v>2190</v>
-      </c>
-      <c r="B1105" t="s">
-        <v>2191</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="B1106" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
+        <v>2192</v>
+      </c>
+      <c r="B1107" t="s">
         <v>2193</v>
-      </c>
-      <c r="B1107" t="s">
-        <v>2194</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
+        <v>2194</v>
+      </c>
+      <c r="B1108" t="s">
         <v>2195</v>
-      </c>
-      <c r="B1108" t="s">
-        <v>2196</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
+        <v>2196</v>
+      </c>
+      <c r="B1109" t="s">
         <v>2197</v>
-      </c>
-      <c r="B1109" t="s">
-        <v>2198</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
       <c r="B1110" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
+        <v>2199</v>
+      </c>
+      <c r="B1111" t="s">
         <v>2200</v>
-      </c>
-      <c r="B1111" t="s">
-        <v>2201</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
+        <v>2201</v>
+      </c>
+      <c r="B1112" t="s">
         <v>2202</v>
-      </c>
-      <c r="B1112" t="s">
-        <v>2203</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
+        <v>2203</v>
+      </c>
+      <c r="B1113" t="s">
         <v>2204</v>
-      </c>
-      <c r="B1113" t="s">
-        <v>2205</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
+        <v>2205</v>
+      </c>
+      <c r="B1114" t="s">
         <v>2206</v>
-      </c>
-      <c r="B1114" t="s">
-        <v>2207</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
+        <v>2207</v>
+      </c>
+      <c r="B1115" t="s">
         <v>2208</v>
-      </c>
-      <c r="B1115" t="s">
-        <v>2209</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
+        <v>2209</v>
+      </c>
+      <c r="B1116" t="s">
         <v>2210</v>
-      </c>
-      <c r="B1116" t="s">
-        <v>2211</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
+        <v>2211</v>
+      </c>
+      <c r="B1117" t="s">
         <v>2212</v>
-      </c>
-      <c r="B1117" t="s">
-        <v>2213</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
+        <v>2213</v>
+      </c>
+      <c r="B1118" t="s">
         <v>2214</v>
-      </c>
-      <c r="B1118" t="s">
-        <v>2215</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
+        <v>2215</v>
+      </c>
+      <c r="B1119" t="s">
         <v>2216</v>
-      </c>
-      <c r="B1119" t="s">
-        <v>2217</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
+        <v>2217</v>
+      </c>
+      <c r="B1120" t="s">
         <v>2218</v>
-      </c>
-      <c r="B1120" t="s">
-        <v>2219</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
+        <v>2219</v>
+      </c>
+      <c r="B1121" t="s">
         <v>2220</v>
-      </c>
-      <c r="B1121" t="s">
-        <v>2221</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
+        <v>2221</v>
+      </c>
+      <c r="B1122" t="s">
         <v>2222</v>
-      </c>
-      <c r="B1122" t="s">
-        <v>2223</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
+        <v>2223</v>
+      </c>
+      <c r="B1123" t="s">
         <v>2224</v>
-      </c>
-      <c r="B1123" t="s">
-        <v>2225</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
+        <v>2225</v>
+      </c>
+      <c r="B1124" t="s">
         <v>2226</v>
-      </c>
-      <c r="B1124" t="s">
-        <v>2227</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
+        <v>2227</v>
+      </c>
+      <c r="B1125" t="s">
         <v>2228</v>
-      </c>
-      <c r="B1125" t="s">
-        <v>2229</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
+        <v>2229</v>
+      </c>
+      <c r="B1126" t="s">
         <v>2230</v>
-      </c>
-      <c r="B1126" t="s">
-        <v>2231</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
+        <v>2231</v>
+      </c>
+      <c r="B1127" t="s">
         <v>2232</v>
-      </c>
-      <c r="B1127" t="s">
-        <v>2233</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
+        <v>2233</v>
+      </c>
+      <c r="B1128" t="s">
         <v>2234</v>
-      </c>
-      <c r="B1128" t="s">
-        <v>2235</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
+        <v>2235</v>
+      </c>
+      <c r="B1129" t="s">
         <v>2236</v>
-      </c>
-      <c r="B1129" t="s">
-        <v>2237</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
+        <v>2237</v>
+      </c>
+      <c r="B1130" t="s">
         <v>2238</v>
-      </c>
-      <c r="B1130" t="s">
-        <v>2239</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
+        <v>2239</v>
+      </c>
+      <c r="B1131" t="s">
         <v>2240</v>
-      </c>
-      <c r="B1131" t="s">
-        <v>2241</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
+        <v>2241</v>
+      </c>
+      <c r="B1132" t="s">
         <v>2242</v>
-      </c>
-      <c r="B1132" t="s">
-        <v>2243</v>
       </c>
     </row>
     <row r="1133" spans="1:2">
       <c r="A1133" t="s">
+        <v>2243</v>
+      </c>
+      <c r="B1133" t="s">
         <v>2244</v>
-      </c>
-      <c r="B1133" t="s">
-        <v>2245</v>
       </c>
     </row>
     <row r="1134" spans="1:2">
       <c r="A1134" t="s">
+        <v>2245</v>
+      </c>
+      <c r="B1134" t="s">
         <v>2246</v>
-      </c>
-      <c r="B1134" t="s">
-        <v>2247</v>
       </c>
     </row>
     <row r="1135" spans="1:2">
       <c r="A1135" t="s">
+        <v>2247</v>
+      </c>
+      <c r="B1135" t="s">
         <v>2248</v>
-      </c>
-      <c r="B1135" t="s">
-        <v>2249</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
+        <v>2249</v>
+      </c>
+      <c r="B1136" t="s">
         <v>2250</v>
-      </c>
-      <c r="B1136" t="s">
-        <v>2251</v>
       </c>
     </row>
     <row r="1137" spans="1:2">
       <c r="A1137" t="s">
+        <v>2251</v>
+      </c>
+      <c r="B1137" t="s">
         <v>2252</v>
-      </c>
-      <c r="B1137" t="s">
-        <v>2253</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
+        <v>2253</v>
+      </c>
+      <c r="B1138" t="s">
         <v>2254</v>
-      </c>
-      <c r="B1138" t="s">
-        <v>2255</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
+        <v>2255</v>
+      </c>
+      <c r="B1139" t="s">
         <v>2256</v>
-      </c>
-      <c r="B1139" t="s">
-        <v>2257</v>
       </c>
     </row>
     <row r="1140" spans="1:2">
       <c r="A1140" t="s">
+        <v>2257</v>
+      </c>
+      <c r="B1140" t="s">
         <v>2258</v>
-      </c>
-      <c r="B1140" t="s">
-        <v>2259</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="B1141" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
+        <v>2260</v>
+      </c>
+      <c r="B1142" t="s">
         <v>2261</v>
-      </c>
-      <c r="B1142" t="s">
-        <v>2262</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
+        <v>2262</v>
+      </c>
+      <c r="B1143" t="s">
         <v>2263</v>
-      </c>
-      <c r="B1143" t="s">
-        <v>2264</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
+        <v>2264</v>
+      </c>
+      <c r="B1144" t="s">
         <v>2265</v>
-      </c>
-      <c r="B1144" t="s">
-        <v>2266</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
+        <v>2266</v>
+      </c>
+      <c r="B1145" t="s">
         <v>2267</v>
-      </c>
-      <c r="B1145" t="s">
-        <v>2268</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
+        <v>2268</v>
+      </c>
+      <c r="B1146" t="s">
         <v>2269</v>
-      </c>
-      <c r="B1146" t="s">
-        <v>2270</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
+        <v>2270</v>
+      </c>
+      <c r="B1147" t="s">
         <v>2271</v>
-      </c>
-      <c r="B1147" t="s">
-        <v>2272</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B1148" t="s">
         <v>2273</v>
-      </c>
-      <c r="B1148" t="s">
-        <v>2274</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
+        <v>2274</v>
+      </c>
+      <c r="B1149" t="s">
         <v>2275</v>
-      </c>
-      <c r="B1149" t="s">
-        <v>2276</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B1150" t="s">
         <v>2277</v>
-      </c>
-      <c r="B1150" t="s">
-        <v>2278</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
+        <v>2278</v>
+      </c>
+      <c r="B1151" t="s">
         <v>2279</v>
-      </c>
-      <c r="B1151" t="s">
-        <v>2280</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
+        <v>2280</v>
+      </c>
+      <c r="B1152" t="s">
         <v>2281</v>
-      </c>
-      <c r="B1152" t="s">
-        <v>2282</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
+        <v>2282</v>
+      </c>
+      <c r="B1153" t="s">
         <v>2283</v>
-      </c>
-      <c r="B1153" t="s">
-        <v>2284</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
+        <v>2284</v>
+      </c>
+      <c r="B1154" t="s">
         <v>2285</v>
-      </c>
-      <c r="B1154" t="s">
-        <v>2286</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
+        <v>2286</v>
+      </c>
+      <c r="B1155" t="s">
         <v>2287</v>
-      </c>
-      <c r="B1155" t="s">
-        <v>2288</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
+        <v>2288</v>
+      </c>
+      <c r="B1156" t="s">
         <v>2289</v>
-      </c>
-      <c r="B1156" t="s">
-        <v>2290</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
+        <v>2290</v>
+      </c>
+      <c r="B1157" t="s">
         <v>2291</v>
-      </c>
-      <c r="B1157" t="s">
-        <v>2292</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
+        <v>2292</v>
+      </c>
+      <c r="B1158" t="s">
         <v>2293</v>
-      </c>
-      <c r="B1158" t="s">
-        <v>2294</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
+        <v>2294</v>
+      </c>
+      <c r="B1159" t="s">
         <v>2295</v>
-      </c>
-      <c r="B1159" t="s">
-        <v>2296</v>
       </c>
     </row>
     <row r="1160" spans="1:2">
       <c r="A1160" t="s">
+        <v>2296</v>
+      </c>
+      <c r="B1160" t="s">
         <v>2297</v>
-      </c>
-      <c r="B1160" t="s">
-        <v>2298</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
+        <v>2298</v>
+      </c>
+      <c r="B1161" t="s">
         <v>2299</v>
-      </c>
-      <c r="B1161" t="s">
-        <v>2300</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" t="s">
+        <v>2300</v>
+      </c>
+      <c r="B1162" t="s">
         <v>2301</v>
-      </c>
-      <c r="B1162" t="s">
-        <v>2302</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
+        <v>2302</v>
+      </c>
+      <c r="B1163" t="s">
         <v>2303</v>
-      </c>
-      <c r="B1163" t="s">
-        <v>2304</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
+        <v>2304</v>
+      </c>
+      <c r="B1164" t="s">
         <v>2305</v>
-      </c>
-      <c r="B1164" t="s">
-        <v>2306</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
+        <v>2306</v>
+      </c>
+      <c r="B1165" t="s">
         <v>2307</v>
-      </c>
-      <c r="B1165" t="s">
-        <v>2308</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
+        <v>2308</v>
+      </c>
+      <c r="B1166" t="s">
         <v>2309</v>
-      </c>
-      <c r="B1166" t="s">
-        <v>2310</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
+        <v>2310</v>
+      </c>
+      <c r="B1167" t="s">
         <v>2311</v>
-      </c>
-      <c r="B1167" t="s">
-        <v>2312</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
+        <v>2312</v>
+      </c>
+      <c r="B1168" t="s">
         <v>2313</v>
-      </c>
-      <c r="B1168" t="s">
-        <v>2314</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
+        <v>2314</v>
+      </c>
+      <c r="B1169" t="s">
         <v>2315</v>
-      </c>
-      <c r="B1169" t="s">
-        <v>2316</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
+        <v>2316</v>
+      </c>
+      <c r="B1170" t="s">
         <v>2317</v>
-      </c>
-      <c r="B1170" t="s">
-        <v>2318</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
+        <v>2318</v>
+      </c>
+      <c r="B1171" t="s">
         <v>2319</v>
-      </c>
-      <c r="B1171" t="s">
-        <v>2320</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
+        <v>2320</v>
+      </c>
+      <c r="B1172" t="s">
         <v>2321</v>
-      </c>
-      <c r="B1172" t="s">
-        <v>2322</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
+        <v>2322</v>
+      </c>
+      <c r="B1173" t="s">
         <v>2323</v>
-      </c>
-      <c r="B1173" t="s">
-        <v>2324</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
+        <v>2324</v>
+      </c>
+      <c r="B1174" t="s">
         <v>2325</v>
-      </c>
-      <c r="B1174" t="s">
-        <v>2326</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
+        <v>2326</v>
+      </c>
+      <c r="B1175" t="s">
         <v>2327</v>
-      </c>
-      <c r="B1175" t="s">
-        <v>2328</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
+        <v>2328</v>
+      </c>
+      <c r="B1176" t="s">
         <v>2329</v>
-      </c>
-      <c r="B1176" t="s">
-        <v>2330</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
+        <v>2330</v>
+      </c>
+      <c r="B1177" t="s">
         <v>2331</v>
-      </c>
-      <c r="B1177" t="s">
-        <v>2332</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
+        <v>2332</v>
+      </c>
+      <c r="B1178" t="s">
         <v>2333</v>
-      </c>
-      <c r="B1178" t="s">
-        <v>2334</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
+        <v>2334</v>
+      </c>
+      <c r="B1179" t="s">
         <v>2335</v>
-      </c>
-      <c r="B1179" t="s">
-        <v>2336</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
+        <v>2336</v>
+      </c>
+      <c r="B1180" t="s">
         <v>2337</v>
-      </c>
-      <c r="B1180" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
@@ -16877,67 +16880,75 @@
         <v>2338</v>
       </c>
       <c r="B1181" t="s">
-        <v>2339</v>
+        <v>912</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
+        <v>2339</v>
+      </c>
+      <c r="B1182" t="s">
         <v>2340</v>
-      </c>
-      <c r="B1182" t="s">
-        <v>2341</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
+        <v>2341</v>
+      </c>
+      <c r="B1183" t="s">
         <v>2342</v>
-      </c>
-      <c r="B1183" t="s">
-        <v>2343</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
+        <v>2343</v>
+      </c>
+      <c r="B1184" t="s">
         <v>2344</v>
-      </c>
-      <c r="B1184" t="s">
-        <v>2345</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
+        <v>2345</v>
+      </c>
+      <c r="B1185" t="s">
         <v>2346</v>
-      </c>
-      <c r="B1185" t="s">
-        <v>2347</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
+        <v>2347</v>
+      </c>
+      <c r="B1186" t="s">
         <v>2348</v>
-      </c>
-      <c r="B1186" t="s">
-        <v>2349</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
+        <v>2349</v>
+      </c>
+      <c r="B1187" t="s">
         <v>2350</v>
-      </c>
-      <c r="B1187" t="s">
-        <v>2351</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
+        <v>2351</v>
+      </c>
+      <c r="B1188" t="s">
         <v>2352</v>
       </c>
-      <c r="B1188" t="s">
+    </row>
+    <row r="1189" spans="1:2">
+      <c r="A1189" t="s">
         <v>2353</v>
       </c>
+      <c r="B1189" t="s">
+        <v>2354</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1188"/>
+  <autoFilter ref="A1:B1189"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ar/headTags.xlsx
+++ b/lang/ar/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1190</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2357">
   <si>
     <t>en</t>
   </si>
@@ -4775,6 +4775,12 @@
   </si>
   <si>
     <t>كائنات مفتوحة المصدر</t>
+  </si>
+  <si>
+    <t>Opus Magnum</t>
+  </si>
+  <si>
+    <t>أوبوس ماغنوم</t>
   </si>
   <si>
     <t>Orb</t>
@@ -7428,7 +7434,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1189"/>
+  <dimension ref="A1:B1190"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13832,15 +13838,15 @@
         <v>1590</v>
       </c>
       <c r="B800" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B801" t="s">
         <v>1591</v>
-      </c>
-      <c r="B801" t="s">
-        <v>1592</v>
       </c>
     </row>
     <row r="802" spans="1:2">
@@ -14464,12 +14470,12 @@
         <v>1747</v>
       </c>
       <c r="B879" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="880" spans="1:2">
       <c r="A880" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="B880" t="s">
         <v>1749</v>
@@ -14536,12 +14542,12 @@
         <v>1764</v>
       </c>
       <c r="B888" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="B889" t="s">
         <v>1766</v>
@@ -14896,12 +14902,12 @@
         <v>1853</v>
       </c>
       <c r="B933" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="B934" t="s">
         <v>1855</v>
@@ -15504,12 +15510,12 @@
         <v>2004</v>
       </c>
       <c r="B1009" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B1010" t="s">
         <v>2006</v>
@@ -15784,12 +15790,12 @@
         <v>2073</v>
       </c>
       <c r="B1044" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="B1045" t="s">
         <v>2075</v>
@@ -15816,12 +15822,12 @@
         <v>2080</v>
       </c>
       <c r="B1048" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="B1049" t="s">
         <v>2082</v>
@@ -15856,12 +15862,12 @@
         <v>2089</v>
       </c>
       <c r="B1053" t="s">
-        <v>2089</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="B1054" t="s">
         <v>2091</v>
@@ -15984,12 +15990,12 @@
         <v>2120</v>
       </c>
       <c r="B1069" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="1070" spans="1:2">
       <c r="A1070" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
       <c r="B1070" t="s">
         <v>2122</v>
@@ -16144,15 +16150,15 @@
         <v>2159</v>
       </c>
       <c r="B1089" t="s">
-        <v>2158</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
+        <v>2161</v>
+      </c>
+      <c r="B1090" t="s">
         <v>2160</v>
-      </c>
-      <c r="B1090" t="s">
-        <v>2161</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
@@ -16248,12 +16254,12 @@
         <v>2184</v>
       </c>
       <c r="B1102" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="B1103" t="s">
         <v>2186</v>
@@ -16280,12 +16286,12 @@
         <v>2191</v>
       </c>
       <c r="B1106" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
       <c r="B1107" t="s">
         <v>2193</v>
@@ -16312,12 +16318,12 @@
         <v>2198</v>
       </c>
       <c r="B1110" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
-        <v>2199</v>
+        <v>2200</v>
       </c>
       <c r="B1111" t="s">
         <v>2200</v>
@@ -16560,12 +16566,12 @@
         <v>2259</v>
       </c>
       <c r="B1141" t="s">
-        <v>2259</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
-        <v>2260</v>
+        <v>2261</v>
       </c>
       <c r="B1142" t="s">
         <v>2261</v>
@@ -16880,15 +16886,15 @@
         <v>2338</v>
       </c>
       <c r="B1181" t="s">
-        <v>912</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>2339</v>
+        <v>2340</v>
       </c>
       <c r="B1182" t="s">
-        <v>2340</v>
+        <v>912</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
@@ -16947,8 +16953,16 @@
         <v>2354</v>
       </c>
     </row>
+    <row r="1190" spans="1:2">
+      <c r="A1190" t="s">
+        <v>2355</v>
+      </c>
+      <c r="B1190" t="s">
+        <v>2356</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1189"/>
+  <autoFilter ref="A1:B1190"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ar/headTags.xlsx
+++ b/lang/ar/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1190</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1191</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2359">
   <si>
     <t>en</t>
   </si>
@@ -989,6 +989,12 @@
   </si>
   <si>
     <t>الكأس</t>
+  </si>
+  <si>
+    <t>Chaos Cubed</t>
+  </si>
+  <si>
+    <t>مكعبات الفوضى</t>
   </si>
   <si>
     <t>Charlie and the Chocolate Factory</t>
@@ -7434,7 +7440,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1190"/>
+  <dimension ref="A1:B1191"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -9302,12 +9308,12 @@
         <v>464</v>
       </c>
       <c r="B233" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="234" spans="1:2">
       <c r="A234" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B234" t="s">
         <v>466</v>
@@ -10022,12 +10028,12 @@
         <v>643</v>
       </c>
       <c r="B323" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="324" spans="1:2">
       <c r="A324" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B324" t="s">
         <v>645</v>
@@ -10126,15 +10132,15 @@
         <v>668</v>
       </c>
       <c r="B336" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="337" spans="1:2">
       <c r="A337" t="s">
+        <v>670</v>
+      </c>
+      <c r="B337" t="s">
         <v>669</v>
-      </c>
-      <c r="B337" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -10294,15 +10300,15 @@
         <v>709</v>
       </c>
       <c r="B357" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
     </row>
     <row r="358" spans="1:2">
       <c r="A358" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B358" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -10742,15 +10748,15 @@
         <v>820</v>
       </c>
       <c r="B413" t="s">
-        <v>791</v>
+        <v>821</v>
       </c>
     </row>
     <row r="414" spans="1:2">
       <c r="A414" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B414" t="s">
-        <v>822</v>
+        <v>793</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -11158,15 +11164,15 @@
         <v>923</v>
       </c>
       <c r="B465" t="s">
-        <v>632</v>
+        <v>924</v>
       </c>
     </row>
     <row r="466" spans="1:2">
       <c r="A466" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B466" t="s">
-        <v>925</v>
+        <v>634</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -11286,12 +11292,12 @@
         <v>954</v>
       </c>
       <c r="B481" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
     </row>
     <row r="482" spans="1:2">
       <c r="A482" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B482" t="s">
         <v>956</v>
@@ -12414,15 +12420,15 @@
         <v>1235</v>
       </c>
       <c r="B622" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="623" spans="1:2">
       <c r="A623" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B623" t="s">
         <v>1236</v>
-      </c>
-      <c r="B623" t="s">
-        <v>1237</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -13846,15 +13852,15 @@
         <v>1592</v>
       </c>
       <c r="B801" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B802" t="s">
         <v>1593</v>
-      </c>
-      <c r="B802" t="s">
-        <v>1594</v>
       </c>
     </row>
     <row r="803" spans="1:2">
@@ -14478,12 +14484,12 @@
         <v>1749</v>
       </c>
       <c r="B880" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="B881" t="s">
         <v>1751</v>
@@ -14550,12 +14556,12 @@
         <v>1766</v>
       </c>
       <c r="B889" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="B890" t="s">
         <v>1768</v>
@@ -14910,12 +14916,12 @@
         <v>1855</v>
       </c>
       <c r="B934" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="B935" t="s">
         <v>1857</v>
@@ -15518,12 +15524,12 @@
         <v>2006</v>
       </c>
       <c r="B1010" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B1011" t="s">
         <v>2008</v>
@@ -15798,12 +15804,12 @@
         <v>2075</v>
       </c>
       <c r="B1045" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="B1046" t="s">
         <v>2077</v>
@@ -15830,12 +15836,12 @@
         <v>2082</v>
       </c>
       <c r="B1049" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="B1050" t="s">
         <v>2084</v>
@@ -15870,12 +15876,12 @@
         <v>2091</v>
       </c>
       <c r="B1054" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="B1055" t="s">
         <v>2093</v>
@@ -15998,12 +16004,12 @@
         <v>2122</v>
       </c>
       <c r="B1070" t="s">
-        <v>2122</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="1071" spans="1:2">
       <c r="A1071" t="s">
-        <v>2123</v>
+        <v>2124</v>
       </c>
       <c r="B1071" t="s">
         <v>2124</v>
@@ -16158,15 +16164,15 @@
         <v>2161</v>
       </c>
       <c r="B1090" t="s">
-        <v>2160</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
+        <v>2163</v>
+      </c>
+      <c r="B1091" t="s">
         <v>2162</v>
-      </c>
-      <c r="B1091" t="s">
-        <v>2163</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
@@ -16262,12 +16268,12 @@
         <v>2186</v>
       </c>
       <c r="B1103" t="s">
-        <v>2186</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="B1104" t="s">
         <v>2188</v>
@@ -16294,12 +16300,12 @@
         <v>2193</v>
       </c>
       <c r="B1107" t="s">
-        <v>2193</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="B1108" t="s">
         <v>2195</v>
@@ -16326,12 +16332,12 @@
         <v>2200</v>
       </c>
       <c r="B1111" t="s">
-        <v>2200</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="B1112" t="s">
         <v>2202</v>
@@ -16574,12 +16580,12 @@
         <v>2261</v>
       </c>
       <c r="B1142" t="s">
-        <v>2261</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>2262</v>
+        <v>2263</v>
       </c>
       <c r="B1143" t="s">
         <v>2263</v>
@@ -16894,15 +16900,15 @@
         <v>2340</v>
       </c>
       <c r="B1182" t="s">
-        <v>912</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>2341</v>
+        <v>2342</v>
       </c>
       <c r="B1183" t="s">
-        <v>2342</v>
+        <v>914</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
@@ -16961,8 +16967,16 @@
         <v>2356</v>
       </c>
     </row>
+    <row r="1191" spans="1:2">
+      <c r="A1191" t="s">
+        <v>2357</v>
+      </c>
+      <c r="B1191" t="s">
+        <v>2358</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1190"/>
+  <autoFilter ref="A1:B1191"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ar/headTags.xlsx
+++ b/lang/ar/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1192</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2361">
   <si>
     <t>en</t>
   </si>
@@ -5168,6 +5168,12 @@
   </si>
   <si>
     <t>ملحمة فريق البوب تيم</t>
+  </si>
+  <si>
+    <t>Popee the Performer</t>
+  </si>
+  <si>
+    <t>بوبي المؤدي</t>
   </si>
   <si>
     <t>POPGOES</t>
@@ -7440,7 +7446,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1191"/>
+  <dimension ref="A1:B1192"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -14492,12 +14498,12 @@
         <v>1751</v>
       </c>
       <c r="B881" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B882" t="s">
         <v>1753</v>
@@ -14564,12 +14570,12 @@
         <v>1768</v>
       </c>
       <c r="B890" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="B891" t="s">
         <v>1770</v>
@@ -14924,12 +14930,12 @@
         <v>1857</v>
       </c>
       <c r="B935" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="B936" t="s">
         <v>1859</v>
@@ -15532,12 +15538,12 @@
         <v>2008</v>
       </c>
       <c r="B1011" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B1012" t="s">
         <v>2010</v>
@@ -15812,12 +15818,12 @@
         <v>2077</v>
       </c>
       <c r="B1046" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="B1047" t="s">
         <v>2079</v>
@@ -15844,12 +15850,12 @@
         <v>2084</v>
       </c>
       <c r="B1050" t="s">
-        <v>2084</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="1051" spans="1:2">
       <c r="A1051" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="B1051" t="s">
         <v>2086</v>
@@ -15884,12 +15890,12 @@
         <v>2093</v>
       </c>
       <c r="B1055" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="B1056" t="s">
         <v>2095</v>
@@ -16012,12 +16018,12 @@
         <v>2124</v>
       </c>
       <c r="B1071" t="s">
-        <v>2124</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="1072" spans="1:2">
       <c r="A1072" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="B1072" t="s">
         <v>2126</v>
@@ -16172,15 +16178,15 @@
         <v>2163</v>
       </c>
       <c r="B1091" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
+        <v>2165</v>
+      </c>
+      <c r="B1092" t="s">
         <v>2164</v>
-      </c>
-      <c r="B1092" t="s">
-        <v>2165</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
@@ -16276,12 +16282,12 @@
         <v>2188</v>
       </c>
       <c r="B1104" t="s">
-        <v>2188</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="B1105" t="s">
         <v>2190</v>
@@ -16308,12 +16314,12 @@
         <v>2195</v>
       </c>
       <c r="B1108" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="B1109" t="s">
         <v>2197</v>
@@ -16340,12 +16346,12 @@
         <v>2202</v>
       </c>
       <c r="B1112" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="B1113" t="s">
         <v>2204</v>
@@ -16588,12 +16594,12 @@
         <v>2263</v>
       </c>
       <c r="B1143" t="s">
-        <v>2263</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="B1144" t="s">
         <v>2265</v>
@@ -16908,15 +16914,15 @@
         <v>2342</v>
       </c>
       <c r="B1183" t="s">
-        <v>914</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>2343</v>
+        <v>2344</v>
       </c>
       <c r="B1184" t="s">
-        <v>2344</v>
+        <v>914</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
@@ -16975,8 +16981,16 @@
         <v>2358</v>
       </c>
     </row>
+    <row r="1192" spans="1:2">
+      <c r="A1192" t="s">
+        <v>2359</v>
+      </c>
+      <c r="B1192" t="s">
+        <v>2360</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1191"/>
+  <autoFilter ref="A1:B1192"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ar/headTags.xlsx
+++ b/lang/ar/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1193</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2363">
   <si>
     <t>en</t>
   </si>
@@ -6434,6 +6434,12 @@
   </si>
   <si>
     <t>تينكرز كونستركت</t>
+  </si>
+  <si>
+    <t>Tiny Takeover</t>
+  </si>
+  <si>
+    <t>استحواذ صغير جداً</t>
   </si>
   <si>
     <t>Titanfall</t>
@@ -7446,7 +7452,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1192"/>
+  <dimension ref="A1:B1193"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -16186,15 +16192,15 @@
         <v>2165</v>
       </c>
       <c r="B1092" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
+        <v>2167</v>
+      </c>
+      <c r="B1093" t="s">
         <v>2166</v>
-      </c>
-      <c r="B1093" t="s">
-        <v>2167</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
@@ -16290,12 +16296,12 @@
         <v>2190</v>
       </c>
       <c r="B1105" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="B1106" t="s">
         <v>2192</v>
@@ -16322,12 +16328,12 @@
         <v>2197</v>
       </c>
       <c r="B1109" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="B1110" t="s">
         <v>2199</v>
@@ -16354,12 +16360,12 @@
         <v>2204</v>
       </c>
       <c r="B1113" t="s">
-        <v>2204</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
       <c r="B1114" t="s">
         <v>2206</v>
@@ -16602,12 +16608,12 @@
         <v>2265</v>
       </c>
       <c r="B1144" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B1145" t="s">
         <v>2267</v>
@@ -16922,15 +16928,15 @@
         <v>2344</v>
       </c>
       <c r="B1184" t="s">
-        <v>914</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>2345</v>
+        <v>2346</v>
       </c>
       <c r="B1185" t="s">
-        <v>2346</v>
+        <v>914</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
@@ -16989,8 +16995,16 @@
         <v>2360</v>
       </c>
     </row>
+    <row r="1193" spans="1:2">
+      <c r="A1193" t="s">
+        <v>2361</v>
+      </c>
+      <c r="B1193" t="s">
+        <v>2362</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1192"/>
+  <autoFilter ref="A1:B1193"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ar/headTags.xlsx
+++ b/lang/ar/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1197</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2371">
   <si>
     <t>en</t>
   </si>
@@ -3472,6 +3472,12 @@
     <t>هايبيكسل</t>
   </si>
   <si>
+    <t>Hypixel (Abiphone)</t>
+  </si>
+  <si>
+    <t>هايبيكسل (أبي فون)</t>
+  </si>
+  <si>
     <t>Hypixel (Attribute Shard)</t>
   </si>
   <si>
@@ -3496,6 +3502,12 @@
     <t>هايبيكسل (العتاد)</t>
   </si>
   <si>
+    <t>Hypixel (Gemstone)</t>
+  </si>
+  <si>
+    <t>هايبيكسل (حجر كريم)</t>
+  </si>
+  <si>
     <t>Hypixel (Minion)</t>
   </si>
   <si>
@@ -3514,6 +3526,12 @@
     <t>هايبيكسل (الشخصيات غير القابلة للعب)</t>
   </si>
   <si>
+    <t>Hypixel (Pet Items)</t>
+  </si>
+  <si>
+    <t>هايبيكسل (عناصر الحيوانات الأليفة)</t>
+  </si>
+  <si>
     <t>Hypixel (Pets)</t>
   </si>
   <si>
@@ -3524,6 +3542,12 @@
   </si>
   <si>
     <t>هايبكسل (حجر إعادة التشكيل)</t>
+  </si>
+  <si>
+    <t>Hypixel (Runes)</t>
+  </si>
+  <si>
+    <t>هيبيكسل (الأحرف الرونية)</t>
   </si>
   <si>
     <t>Hypixel (Sacks)</t>
@@ -7452,7 +7476,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1193"/>
+  <dimension ref="A1:B1197"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -12440,39 +12464,39 @@
         <v>1237</v>
       </c>
       <c r="B623" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="624" spans="1:2">
       <c r="A624" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B624" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="625" spans="1:2">
       <c r="A625" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="B625" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="626" spans="1:2">
       <c r="A626" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B626" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="627" spans="1:2">
       <c r="A627" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B627" t="s">
         <v>1244</v>
-      </c>
-      <c r="B627" t="s">
-        <v>1245</v>
       </c>
     </row>
     <row r="628" spans="1:2">
@@ -13872,39 +13896,39 @@
         <v>1594</v>
       </c>
       <c r="B802" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="B803" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="B804" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="B805" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B806" t="s">
         <v>1601</v>
-      </c>
-      <c r="B806" t="s">
-        <v>1602</v>
       </c>
     </row>
     <row r="807" spans="1:2">
@@ -14512,36 +14536,36 @@
         <v>1753</v>
       </c>
       <c r="B882" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="883" spans="1:2">
       <c r="A883" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="B883" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="884" spans="1:2">
       <c r="A884" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="B884" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="885" spans="1:2">
       <c r="A885" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="B885" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B886" t="s">
         <v>1761</v>
@@ -14584,36 +14608,36 @@
         <v>1770</v>
       </c>
       <c r="B891" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="B892" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="B893" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="B894" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="B895" t="s">
         <v>1778</v>
@@ -14944,36 +14968,36 @@
         <v>1859</v>
       </c>
       <c r="B936" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="937" spans="1:2">
       <c r="A937" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="B937" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="938" spans="1:2">
       <c r="A938" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B938" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="939" spans="1:2">
       <c r="A939" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="B939" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="940" spans="1:2">
       <c r="A940" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="B940" t="s">
         <v>1867</v>
@@ -15552,36 +15576,36 @@
         <v>2010</v>
       </c>
       <c r="B1012" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B1013" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B1014" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B1015" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B1016" t="s">
         <v>2018</v>
@@ -15832,68 +15856,68 @@
         <v>2079</v>
       </c>
       <c r="B1047" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="B1048" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="B1049" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="B1050" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="1051" spans="1:2">
       <c r="A1051" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="B1051" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="B1052" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
-        <v>2089</v>
+        <v>2090</v>
       </c>
       <c r="B1053" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="B1054" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="B1055" t="s">
         <v>2094</v>
@@ -15904,36 +15928,36 @@
         <v>2095</v>
       </c>
       <c r="B1056" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="B1057" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="B1058" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="B1059" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="B1060" t="s">
         <v>2103</v>
@@ -16032,36 +16056,36 @@
         <v>2126</v>
       </c>
       <c r="B1072" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="1073" spans="1:2">
       <c r="A1073" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
       <c r="B1073" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="1074" spans="1:2">
       <c r="A1074" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="B1074" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="B1075" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="B1076" t="s">
         <v>2134</v>
@@ -16200,39 +16224,39 @@
         <v>2167</v>
       </c>
       <c r="B1093" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
       <c r="B1094" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>2170</v>
+        <v>2171</v>
       </c>
       <c r="B1095" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="B1096" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
+        <v>2175</v>
+      </c>
+      <c r="B1097" t="s">
         <v>2174</v>
-      </c>
-      <c r="B1097" t="s">
-        <v>2175</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
@@ -16304,100 +16328,100 @@
         <v>2192</v>
       </c>
       <c r="B1106" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>2193</v>
+        <v>2194</v>
       </c>
       <c r="B1107" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="B1108" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="B1109" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
-        <v>2199</v>
+        <v>2200</v>
       </c>
       <c r="B1110" t="s">
-        <v>2199</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="B1111" t="s">
-        <v>2201</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="B1112" t="s">
-        <v>2203</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="B1113" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>2206</v>
+        <v>2207</v>
       </c>
       <c r="B1114" t="s">
-        <v>2206</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>2207</v>
+        <v>2208</v>
       </c>
       <c r="B1115" t="s">
-        <v>2208</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>2209</v>
+        <v>2210</v>
       </c>
       <c r="B1116" t="s">
-        <v>2210</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>2211</v>
+        <v>2212</v>
       </c>
       <c r="B1117" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>2213</v>
+        <v>2214</v>
       </c>
       <c r="B1118" t="s">
         <v>2214</v>
@@ -16616,36 +16640,36 @@
         <v>2267</v>
       </c>
       <c r="B1145" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
-        <v>2268</v>
+        <v>2269</v>
       </c>
       <c r="B1146" t="s">
-        <v>2269</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>2270</v>
+        <v>2271</v>
       </c>
       <c r="B1147" t="s">
-        <v>2271</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>2272</v>
+        <v>2273</v>
       </c>
       <c r="B1148" t="s">
-        <v>2273</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>2274</v>
+        <v>2275</v>
       </c>
       <c r="B1149" t="s">
         <v>2275</v>
@@ -16936,39 +16960,39 @@
         <v>2346</v>
       </c>
       <c r="B1185" t="s">
-        <v>914</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>2347</v>
+        <v>2348</v>
       </c>
       <c r="B1186" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
       <c r="B1187" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>2351</v>
+        <v>2352</v>
       </c>
       <c r="B1188" t="s">
-        <v>2352</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>2353</v>
+        <v>2354</v>
       </c>
       <c r="B1189" t="s">
-        <v>2354</v>
+        <v>914</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
@@ -17003,8 +17027,40 @@
         <v>2362</v>
       </c>
     </row>
+    <row r="1194" spans="1:2">
+      <c r="A1194" t="s">
+        <v>2363</v>
+      </c>
+      <c r="B1194" t="s">
+        <v>2364</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:2">
+      <c r="A1195" t="s">
+        <v>2365</v>
+      </c>
+      <c r="B1195" t="s">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:2">
+      <c r="A1196" t="s">
+        <v>2367</v>
+      </c>
+      <c r="B1196" t="s">
+        <v>2368</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:2">
+      <c r="A1197" t="s">
+        <v>2369</v>
+      </c>
+      <c r="B1197" t="s">
+        <v>2370</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1193"/>
+  <autoFilter ref="A1:B1197"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ar/headTags.xlsx
+++ b/lang/ar/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1197</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1198</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2373">
   <si>
     <t>en</t>
   </si>
@@ -5276,6 +5276,12 @@
   </si>
   <si>
     <t>البروفيسور لايتون</t>
+  </si>
+  <si>
+    <t>Project Zomboid</t>
+  </si>
+  <si>
+    <t>مشروع زومبويد</t>
   </si>
   <si>
     <t>Pumpkin</t>
@@ -7476,7 +7482,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1197"/>
+  <dimension ref="A1:B1198"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -14568,12 +14574,12 @@
         <v>1761</v>
       </c>
       <c r="B886" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="B887" t="s">
         <v>1763</v>
@@ -14640,12 +14646,12 @@
         <v>1778</v>
       </c>
       <c r="B895" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="B896" t="s">
         <v>1780</v>
@@ -15000,12 +15006,12 @@
         <v>1867</v>
       </c>
       <c r="B940" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="941" spans="1:2">
       <c r="A941" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="B941" t="s">
         <v>1869</v>
@@ -15608,12 +15614,12 @@
         <v>2018</v>
       </c>
       <c r="B1016" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B1017" t="s">
         <v>2020</v>
@@ -15888,12 +15894,12 @@
         <v>2087</v>
       </c>
       <c r="B1051" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="B1052" t="s">
         <v>2089</v>
@@ -15920,12 +15926,12 @@
         <v>2094</v>
       </c>
       <c r="B1055" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
       <c r="B1056" t="s">
         <v>2096</v>
@@ -15960,12 +15966,12 @@
         <v>2103</v>
       </c>
       <c r="B1060" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
       <c r="A1061" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="B1061" t="s">
         <v>2105</v>
@@ -16088,12 +16094,12 @@
         <v>2134</v>
       </c>
       <c r="B1076" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="1077" spans="1:2">
       <c r="A1077" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="B1077" t="s">
         <v>2136</v>
@@ -16256,15 +16262,15 @@
         <v>2175</v>
       </c>
       <c r="B1097" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
+        <v>2177</v>
+      </c>
+      <c r="B1098" t="s">
         <v>2176</v>
-      </c>
-      <c r="B1098" t="s">
-        <v>2177</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
@@ -16360,12 +16366,12 @@
         <v>2200</v>
       </c>
       <c r="B1110" t="s">
-        <v>2200</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="B1111" t="s">
         <v>2202</v>
@@ -16392,12 +16398,12 @@
         <v>2207</v>
       </c>
       <c r="B1114" t="s">
-        <v>2207</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>2208</v>
+        <v>2209</v>
       </c>
       <c r="B1115" t="s">
         <v>2209</v>
@@ -16424,12 +16430,12 @@
         <v>2214</v>
       </c>
       <c r="B1118" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
       <c r="B1119" t="s">
         <v>2216</v>
@@ -16672,12 +16678,12 @@
         <v>2275</v>
       </c>
       <c r="B1149" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
       <c r="B1150" t="s">
         <v>2277</v>
@@ -16992,15 +16998,15 @@
         <v>2354</v>
       </c>
       <c r="B1189" t="s">
-        <v>914</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
       <c r="A1190" t="s">
-        <v>2355</v>
+        <v>2356</v>
       </c>
       <c r="B1190" t="s">
-        <v>2356</v>
+        <v>914</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
@@ -17059,8 +17065,16 @@
         <v>2370</v>
       </c>
     </row>
+    <row r="1198" spans="1:2">
+      <c r="A1198" t="s">
+        <v>2371</v>
+      </c>
+      <c r="B1198" t="s">
+        <v>2372</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1197"/>
+  <autoFilter ref="A1:B1198"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ar/headTags.xlsx
+++ b/lang/ar/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1198</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1199</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2375">
   <si>
     <t>en</t>
   </si>
@@ -425,6 +425,12 @@
   </si>
   <si>
     <t>باكا واختبار</t>
+  </si>
+  <si>
+    <t>Bakugan</t>
+  </si>
+  <si>
+    <t>باكوغان</t>
   </si>
   <si>
     <t>Baldi's Basics</t>
@@ -7482,7 +7488,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1198"/>
+  <dimension ref="A1:B1199"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -9358,12 +9364,12 @@
         <v>466</v>
       </c>
       <c r="B234" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="235" spans="1:2">
       <c r="A235" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B235" t="s">
         <v>468</v>
@@ -10078,12 +10084,12 @@
         <v>645</v>
       </c>
       <c r="B324" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="325" spans="1:2">
       <c r="A325" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B325" t="s">
         <v>647</v>
@@ -10182,15 +10188,15 @@
         <v>670</v>
       </c>
       <c r="B337" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="338" spans="1:2">
       <c r="A338" t="s">
+        <v>672</v>
+      </c>
+      <c r="B338" t="s">
         <v>671</v>
-      </c>
-      <c r="B338" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -10350,15 +10356,15 @@
         <v>711</v>
       </c>
       <c r="B358" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
     </row>
     <row r="359" spans="1:2">
       <c r="A359" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B359" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -10798,15 +10804,15 @@
         <v>822</v>
       </c>
       <c r="B414" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
     </row>
     <row r="415" spans="1:2">
       <c r="A415" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B415" t="s">
-        <v>824</v>
+        <v>795</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -11214,15 +11220,15 @@
         <v>925</v>
       </c>
       <c r="B466" t="s">
-        <v>634</v>
+        <v>926</v>
       </c>
     </row>
     <row r="467" spans="1:2">
       <c r="A467" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B467" t="s">
-        <v>927</v>
+        <v>636</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -11342,12 +11348,12 @@
         <v>956</v>
       </c>
       <c r="B482" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="483" spans="1:2">
       <c r="A483" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B483" t="s">
         <v>958</v>
@@ -12502,15 +12508,15 @@
         <v>1245</v>
       </c>
       <c r="B627" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="628" spans="1:2">
       <c r="A628" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B628" t="s">
         <v>1246</v>
-      </c>
-      <c r="B628" t="s">
-        <v>1247</v>
       </c>
     </row>
     <row r="629" spans="1:2">
@@ -13934,15 +13940,15 @@
         <v>1602</v>
       </c>
       <c r="B806" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="807" spans="1:2">
       <c r="A807" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B807" t="s">
         <v>1603</v>
-      </c>
-      <c r="B807" t="s">
-        <v>1604</v>
       </c>
     </row>
     <row r="808" spans="1:2">
@@ -14582,12 +14588,12 @@
         <v>1763</v>
       </c>
       <c r="B887" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="B888" t="s">
         <v>1765</v>
@@ -14654,12 +14660,12 @@
         <v>1780</v>
       </c>
       <c r="B896" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="B897" t="s">
         <v>1782</v>
@@ -15014,12 +15020,12 @@
         <v>1869</v>
       </c>
       <c r="B941" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="942" spans="1:2">
       <c r="A942" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="B942" t="s">
         <v>1871</v>
@@ -15622,12 +15628,12 @@
         <v>2020</v>
       </c>
       <c r="B1017" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B1018" t="s">
         <v>2022</v>
@@ -15902,12 +15908,12 @@
         <v>2089</v>
       </c>
       <c r="B1052" t="s">
-        <v>2089</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="B1053" t="s">
         <v>2091</v>
@@ -15934,12 +15940,12 @@
         <v>2096</v>
       </c>
       <c r="B1056" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="B1057" t="s">
         <v>2098</v>
@@ -15974,12 +15980,12 @@
         <v>2105</v>
       </c>
       <c r="B1061" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="B1062" t="s">
         <v>2107</v>
@@ -16102,12 +16108,12 @@
         <v>2136</v>
       </c>
       <c r="B1077" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
       <c r="B1078" t="s">
         <v>2138</v>
@@ -16270,15 +16276,15 @@
         <v>2177</v>
       </c>
       <c r="B1098" t="s">
-        <v>2176</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
+        <v>2179</v>
+      </c>
+      <c r="B1099" t="s">
         <v>2178</v>
-      </c>
-      <c r="B1099" t="s">
-        <v>2179</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
@@ -16374,12 +16380,12 @@
         <v>2202</v>
       </c>
       <c r="B1111" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="B1112" t="s">
         <v>2204</v>
@@ -16406,12 +16412,12 @@
         <v>2209</v>
       </c>
       <c r="B1115" t="s">
-        <v>2209</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="B1116" t="s">
         <v>2211</v>
@@ -16438,12 +16444,12 @@
         <v>2216</v>
       </c>
       <c r="B1119" t="s">
-        <v>2216</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>2217</v>
+        <v>2218</v>
       </c>
       <c r="B1120" t="s">
         <v>2218</v>
@@ -16686,12 +16692,12 @@
         <v>2277</v>
       </c>
       <c r="B1150" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>2278</v>
+        <v>2279</v>
       </c>
       <c r="B1151" t="s">
         <v>2279</v>
@@ -17006,15 +17012,15 @@
         <v>2356</v>
       </c>
       <c r="B1190" t="s">
-        <v>914</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
       <c r="A1191" t="s">
-        <v>2357</v>
+        <v>2358</v>
       </c>
       <c r="B1191" t="s">
-        <v>2358</v>
+        <v>916</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
@@ -17073,8 +17079,16 @@
         <v>2372</v>
       </c>
     </row>
+    <row r="1199" spans="1:2">
+      <c r="A1199" t="s">
+        <v>2373</v>
+      </c>
+      <c r="B1199" t="s">
+        <v>2374</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1198"/>
+  <autoFilter ref="A1:B1199"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ar/headTags.xlsx
+++ b/lang/ar/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1199</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1200</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2377">
   <si>
     <t>en</t>
   </si>
@@ -5669,6 +5669,12 @@
   </si>
   <si>
     <t>ظلال موردور</t>
+  </si>
+  <si>
+    <t>Shark</t>
+  </si>
+  <si>
+    <t>القرش</t>
   </si>
   <si>
     <t>Sheep</t>
@@ -7488,7 +7494,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1199"/>
+  <dimension ref="A1:B1200"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -15636,12 +15642,12 @@
         <v>2022</v>
       </c>
       <c r="B1018" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B1019" t="s">
         <v>2024</v>
@@ -15916,12 +15922,12 @@
         <v>2091</v>
       </c>
       <c r="B1053" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="B1054" t="s">
         <v>2093</v>
@@ -15948,12 +15954,12 @@
         <v>2098</v>
       </c>
       <c r="B1057" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="B1058" t="s">
         <v>2100</v>
@@ -15988,12 +15994,12 @@
         <v>2107</v>
       </c>
       <c r="B1062" t="s">
-        <v>2107</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="B1063" t="s">
         <v>2109</v>
@@ -16116,12 +16122,12 @@
         <v>2138</v>
       </c>
       <c r="B1078" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="B1079" t="s">
         <v>2140</v>
@@ -16284,15 +16290,15 @@
         <v>2179</v>
       </c>
       <c r="B1099" t="s">
-        <v>2178</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B1100" t="s">
         <v>2180</v>
-      </c>
-      <c r="B1100" t="s">
-        <v>2181</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
@@ -16388,12 +16394,12 @@
         <v>2204</v>
       </c>
       <c r="B1112" t="s">
-        <v>2204</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
       <c r="B1113" t="s">
         <v>2206</v>
@@ -16420,12 +16426,12 @@
         <v>2211</v>
       </c>
       <c r="B1116" t="s">
-        <v>2211</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
       <c r="B1117" t="s">
         <v>2213</v>
@@ -16452,12 +16458,12 @@
         <v>2218</v>
       </c>
       <c r="B1120" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="B1121" t="s">
         <v>2220</v>
@@ -16700,12 +16706,12 @@
         <v>2279</v>
       </c>
       <c r="B1151" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="B1152" t="s">
         <v>2281</v>
@@ -17020,15 +17026,15 @@
         <v>2358</v>
       </c>
       <c r="B1191" t="s">
-        <v>916</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
       <c r="A1192" t="s">
-        <v>2359</v>
+        <v>2360</v>
       </c>
       <c r="B1192" t="s">
-        <v>2360</v>
+        <v>916</v>
       </c>
     </row>
     <row r="1193" spans="1:2">
@@ -17087,8 +17093,16 @@
         <v>2374</v>
       </c>
     </row>
+    <row r="1200" spans="1:2">
+      <c r="A1200" t="s">
+        <v>2375</v>
+      </c>
+      <c r="B1200" t="s">
+        <v>2376</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1199"/>
+  <autoFilter ref="A1:B1200"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ar/headTags.xlsx
+++ b/lang/ar/headTags.xlsx
@@ -1960,6 +1960,12 @@
     <t>حكايات الجنيات</t>
   </si>
   <si>
+    <t>Fall Drop</t>
+  </si>
+  <si>
+    <t>سقوط الخريف</t>
+  </si>
+  <si>
     <t>Fall Guys</t>
   </si>
   <si>
@@ -7079,12 +7085,6 @@
   </si>
   <si>
     <t>علامة Hypixel (الطفرات)</t>
-  </si>
-  <si>
-    <t>Fall Drop</t>
-  </si>
-  <si>
-    <t>سقوط الخريف</t>
   </si>
   <si>
     <t>Summer Drop 2025</t>
@@ -10098,12 +10098,12 @@
         <v>647</v>
       </c>
       <c r="B325" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="326" spans="1:2">
       <c r="A326" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B326" t="s">
         <v>649</v>
@@ -10202,15 +10202,15 @@
         <v>672</v>
       </c>
       <c r="B338" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="339" spans="1:2">
       <c r="A339" t="s">
+        <v>674</v>
+      </c>
+      <c r="B339" t="s">
         <v>673</v>
-      </c>
-      <c r="B339" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -10370,15 +10370,15 @@
         <v>713</v>
       </c>
       <c r="B359" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
     </row>
     <row r="360" spans="1:2">
       <c r="A360" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B360" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -10818,15 +10818,15 @@
         <v>824</v>
       </c>
       <c r="B415" t="s">
-        <v>795</v>
+        <v>825</v>
       </c>
     </row>
     <row r="416" spans="1:2">
       <c r="A416" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B416" t="s">
-        <v>826</v>
+        <v>797</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -11234,15 +11234,15 @@
         <v>927</v>
       </c>
       <c r="B467" t="s">
-        <v>636</v>
+        <v>928</v>
       </c>
     </row>
     <row r="468" spans="1:2">
       <c r="A468" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B468" t="s">
-        <v>929</v>
+        <v>636</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -11362,12 +11362,12 @@
         <v>958</v>
       </c>
       <c r="B483" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
     </row>
     <row r="484" spans="1:2">
       <c r="A484" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B484" t="s">
         <v>960</v>
@@ -12522,15 +12522,15 @@
         <v>1247</v>
       </c>
       <c r="B628" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="629" spans="1:2">
       <c r="A629" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B629" t="s">
         <v>1248</v>
-      </c>
-      <c r="B629" t="s">
-        <v>1249</v>
       </c>
     </row>
     <row r="630" spans="1:2">
@@ -13954,15 +13954,15 @@
         <v>1604</v>
       </c>
       <c r="B807" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B808" t="s">
         <v>1605</v>
-      </c>
-      <c r="B808" t="s">
-        <v>1606</v>
       </c>
     </row>
     <row r="809" spans="1:2">
@@ -14602,12 +14602,12 @@
         <v>1765</v>
       </c>
       <c r="B888" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="B889" t="s">
         <v>1767</v>
@@ -14674,12 +14674,12 @@
         <v>1782</v>
       </c>
       <c r="B897" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="B898" t="s">
         <v>1784</v>
@@ -15034,12 +15034,12 @@
         <v>1871</v>
       </c>
       <c r="B942" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="943" spans="1:2">
       <c r="A943" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="B943" t="s">
         <v>1873</v>
@@ -15650,12 +15650,12 @@
         <v>2024</v>
       </c>
       <c r="B1019" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B1020" t="s">
         <v>2026</v>
@@ -15930,12 +15930,12 @@
         <v>2093</v>
       </c>
       <c r="B1054" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="B1055" t="s">
         <v>2095</v>
@@ -15962,12 +15962,12 @@
         <v>2100</v>
       </c>
       <c r="B1058" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="B1059" t="s">
         <v>2102</v>
@@ -16002,12 +16002,12 @@
         <v>2109</v>
       </c>
       <c r="B1063" t="s">
-        <v>2109</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="B1064" t="s">
         <v>2111</v>
@@ -16130,12 +16130,12 @@
         <v>2140</v>
       </c>
       <c r="B1079" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="1080" spans="1:2">
       <c r="A1080" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="B1080" t="s">
         <v>2142</v>
@@ -16298,15 +16298,15 @@
         <v>2181</v>
       </c>
       <c r="B1100" t="s">
-        <v>2180</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
+        <v>2183</v>
+      </c>
+      <c r="B1101" t="s">
         <v>2182</v>
-      </c>
-      <c r="B1101" t="s">
-        <v>2183</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
@@ -16402,12 +16402,12 @@
         <v>2206</v>
       </c>
       <c r="B1113" t="s">
-        <v>2206</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>2207</v>
+        <v>2208</v>
       </c>
       <c r="B1114" t="s">
         <v>2208</v>
@@ -16434,12 +16434,12 @@
         <v>2213</v>
       </c>
       <c r="B1117" t="s">
-        <v>2213</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
       <c r="B1118" t="s">
         <v>2215</v>
@@ -16466,12 +16466,12 @@
         <v>2220</v>
       </c>
       <c r="B1121" t="s">
-        <v>2220</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>2221</v>
+        <v>2222</v>
       </c>
       <c r="B1122" t="s">
         <v>2222</v>
@@ -16714,12 +16714,12 @@
         <v>2281</v>
       </c>
       <c r="B1152" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>2282</v>
+        <v>2283</v>
       </c>
       <c r="B1153" t="s">
         <v>2283</v>
@@ -17034,7 +17034,7 @@
         <v>2360</v>
       </c>
       <c r="B1192" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
     </row>
     <row r="1193" spans="1:2">

--- a/lang/ar/headTags.xlsx
+++ b/lang/ar/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1201</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2379">
   <si>
     <t>en</t>
   </si>
@@ -5258,6 +5258,12 @@
   </si>
   <si>
     <t>بريداتور</t>
+  </si>
+  <si>
+    <t>Prehistoric Creature</t>
+  </si>
+  <si>
+    <t>مخلوق من العصور ما قبل التاريخ</t>
   </si>
   <si>
     <t>Present</t>
@@ -7494,7 +7500,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1200"/>
+  <dimension ref="A1:B1201"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -14610,12 +14616,12 @@
         <v>1767</v>
       </c>
       <c r="B889" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="B890" t="s">
         <v>1769</v>
@@ -14682,12 +14688,12 @@
         <v>1784</v>
       </c>
       <c r="B898" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="899" spans="1:2">
       <c r="A899" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="B899" t="s">
         <v>1786</v>
@@ -15042,12 +15048,12 @@
         <v>1873</v>
       </c>
       <c r="B943" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="B944" t="s">
         <v>1875</v>
@@ -15658,12 +15664,12 @@
         <v>2026</v>
       </c>
       <c r="B1020" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="B1021" t="s">
         <v>2028</v>
@@ -15938,12 +15944,12 @@
         <v>2095</v>
       </c>
       <c r="B1055" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="B1056" t="s">
         <v>2097</v>
@@ -15970,12 +15976,12 @@
         <v>2102</v>
       </c>
       <c r="B1059" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="B1060" t="s">
         <v>2104</v>
@@ -16010,12 +16016,12 @@
         <v>2111</v>
       </c>
       <c r="B1064" t="s">
-        <v>2111</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="1065" spans="1:2">
       <c r="A1065" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="B1065" t="s">
         <v>2113</v>
@@ -16138,12 +16144,12 @@
         <v>2142</v>
       </c>
       <c r="B1080" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="B1081" t="s">
         <v>2144</v>
@@ -16306,15 +16312,15 @@
         <v>2183</v>
       </c>
       <c r="B1101" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
       <c r="A1102" t="s">
+        <v>2185</v>
+      </c>
+      <c r="B1102" t="s">
         <v>2184</v>
-      </c>
-      <c r="B1102" t="s">
-        <v>2185</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
@@ -16410,12 +16416,12 @@
         <v>2208</v>
       </c>
       <c r="B1114" t="s">
-        <v>2208</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>2209</v>
+        <v>2210</v>
       </c>
       <c r="B1115" t="s">
         <v>2210</v>
@@ -16442,12 +16448,12 @@
         <v>2215</v>
       </c>
       <c r="B1118" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>2216</v>
+        <v>2217</v>
       </c>
       <c r="B1119" t="s">
         <v>2217</v>
@@ -16474,12 +16480,12 @@
         <v>2222</v>
       </c>
       <c r="B1122" t="s">
-        <v>2222</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
-        <v>2223</v>
+        <v>2224</v>
       </c>
       <c r="B1123" t="s">
         <v>2224</v>
@@ -16722,12 +16728,12 @@
         <v>2283</v>
       </c>
       <c r="B1153" t="s">
-        <v>2283</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>2284</v>
+        <v>2285</v>
       </c>
       <c r="B1154" t="s">
         <v>2285</v>
@@ -17034,15 +17040,15 @@
         <v>2360</v>
       </c>
       <c r="B1192" t="s">
-        <v>918</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="1193" spans="1:2">
       <c r="A1193" t="s">
-        <v>2361</v>
+        <v>2362</v>
       </c>
       <c r="B1193" t="s">
-        <v>2362</v>
+        <v>918</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
@@ -17101,8 +17107,16 @@
         <v>2376</v>
       </c>
     </row>
+    <row r="1201" spans="1:2">
+      <c r="A1201" t="s">
+        <v>2377</v>
+      </c>
+      <c r="B1201" t="s">
+        <v>2378</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1200"/>
+  <autoFilter ref="A1:B1201"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ar/headTags.xlsx
+++ b/lang/ar/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1202</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2381">
   <si>
     <t>en</t>
   </si>
@@ -413,6 +413,12 @@
   </si>
   <si>
     <t>العودة إلى المستقبل</t>
+  </si>
+  <si>
+    <t>Backrooms (Movie)</t>
+  </si>
+  <si>
+    <t>«باكروومز» (فيلم)</t>
   </si>
   <si>
     <t>Bag</t>
@@ -7500,7 +7506,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1201"/>
+  <dimension ref="A1:B1202"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -9384,12 +9390,12 @@
         <v>468</v>
       </c>
       <c r="B235" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="236" spans="1:2">
       <c r="A236" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B236" t="s">
         <v>470</v>
@@ -10112,12 +10118,12 @@
         <v>649</v>
       </c>
       <c r="B326" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="327" spans="1:2">
       <c r="A327" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B327" t="s">
         <v>651</v>
@@ -10216,15 +10222,15 @@
         <v>674</v>
       </c>
       <c r="B339" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="340" spans="1:2">
       <c r="A340" t="s">
+        <v>676</v>
+      </c>
+      <c r="B340" t="s">
         <v>675</v>
-      </c>
-      <c r="B340" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -10384,15 +10390,15 @@
         <v>715</v>
       </c>
       <c r="B360" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
     </row>
     <row r="361" spans="1:2">
       <c r="A361" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B361" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -10832,15 +10838,15 @@
         <v>826</v>
       </c>
       <c r="B416" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
     </row>
     <row r="417" spans="1:2">
       <c r="A417" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B417" t="s">
-        <v>828</v>
+        <v>799</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -11248,15 +11254,15 @@
         <v>929</v>
       </c>
       <c r="B468" t="s">
-        <v>636</v>
+        <v>930</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B469" t="s">
-        <v>931</v>
+        <v>638</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -11376,12 +11382,12 @@
         <v>960</v>
       </c>
       <c r="B484" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="485" spans="1:2">
       <c r="A485" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B485" t="s">
         <v>962</v>
@@ -12536,15 +12542,15 @@
         <v>1249</v>
       </c>
       <c r="B629" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="630" spans="1:2">
       <c r="A630" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B630" t="s">
         <v>1250</v>
-      </c>
-      <c r="B630" t="s">
-        <v>1251</v>
       </c>
     </row>
     <row r="631" spans="1:2">
@@ -13968,15 +13974,15 @@
         <v>1606</v>
       </c>
       <c r="B808" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="809" spans="1:2">
       <c r="A809" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B809" t="s">
         <v>1607</v>
-      </c>
-      <c r="B809" t="s">
-        <v>1608</v>
       </c>
     </row>
     <row r="810" spans="1:2">
@@ -14624,12 +14630,12 @@
         <v>1769</v>
       </c>
       <c r="B890" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="B891" t="s">
         <v>1771</v>
@@ -14696,12 +14702,12 @@
         <v>1786</v>
       </c>
       <c r="B899" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="B900" t="s">
         <v>1788</v>
@@ -15056,12 +15062,12 @@
         <v>1875</v>
       </c>
       <c r="B944" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="B945" t="s">
         <v>1877</v>
@@ -15672,12 +15678,12 @@
         <v>2028</v>
       </c>
       <c r="B1021" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="B1022" t="s">
         <v>2030</v>
@@ -15952,12 +15958,12 @@
         <v>2097</v>
       </c>
       <c r="B1056" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="B1057" t="s">
         <v>2099</v>
@@ -15984,12 +15990,12 @@
         <v>2104</v>
       </c>
       <c r="B1060" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
       <c r="A1061" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="B1061" t="s">
         <v>2106</v>
@@ -16024,12 +16030,12 @@
         <v>2113</v>
       </c>
       <c r="B1065" t="s">
-        <v>2113</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" t="s">
-        <v>2114</v>
+        <v>2115</v>
       </c>
       <c r="B1066" t="s">
         <v>2115</v>
@@ -16152,12 +16158,12 @@
         <v>2144</v>
       </c>
       <c r="B1081" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="B1082" t="s">
         <v>2146</v>
@@ -16320,15 +16326,15 @@
         <v>2185</v>
       </c>
       <c r="B1102" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
+        <v>2187</v>
+      </c>
+      <c r="B1103" t="s">
         <v>2186</v>
-      </c>
-      <c r="B1103" t="s">
-        <v>2187</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
@@ -16424,12 +16430,12 @@
         <v>2210</v>
       </c>
       <c r="B1115" t="s">
-        <v>2210</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>2211</v>
+        <v>2212</v>
       </c>
       <c r="B1116" t="s">
         <v>2212</v>
@@ -16456,12 +16462,12 @@
         <v>2217</v>
       </c>
       <c r="B1119" t="s">
-        <v>2217</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
       <c r="B1120" t="s">
         <v>2219</v>
@@ -16488,12 +16494,12 @@
         <v>2224</v>
       </c>
       <c r="B1123" t="s">
-        <v>2224</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
-        <v>2225</v>
+        <v>2226</v>
       </c>
       <c r="B1124" t="s">
         <v>2226</v>
@@ -16736,12 +16742,12 @@
         <v>2285</v>
       </c>
       <c r="B1154" t="s">
-        <v>2285</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>2286</v>
+        <v>2287</v>
       </c>
       <c r="B1155" t="s">
         <v>2287</v>
@@ -17048,15 +17054,15 @@
         <v>2362</v>
       </c>
       <c r="B1193" t="s">
-        <v>918</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
       <c r="A1194" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="B1194" t="s">
-        <v>2364</v>
+        <v>920</v>
       </c>
     </row>
     <row r="1195" spans="1:2">
@@ -17115,8 +17121,16 @@
         <v>2378</v>
       </c>
     </row>
+    <row r="1202" spans="1:2">
+      <c r="A1202" t="s">
+        <v>2379</v>
+      </c>
+      <c r="B1202" t="s">
+        <v>2380</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1201"/>
+  <autoFilter ref="A1:B1202"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ar/headTags.xlsx
+++ b/lang/ar/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1202</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1203</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2383">
   <si>
     <t>en</t>
   </si>
@@ -1544,6 +1544,12 @@
   </si>
   <si>
     <t>ديابلو</t>
+  </si>
+  <si>
+    <t>Die of Death</t>
+  </si>
+  <si>
+    <t>قالب الموت</t>
   </si>
   <si>
     <t>Digimon</t>
@@ -7506,7 +7512,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1202"/>
+  <dimension ref="A1:B1203"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -10126,12 +10132,12 @@
         <v>651</v>
       </c>
       <c r="B327" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="328" spans="1:2">
       <c r="A328" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B328" t="s">
         <v>653</v>
@@ -10230,15 +10236,15 @@
         <v>676</v>
       </c>
       <c r="B340" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="341" spans="1:2">
       <c r="A341" t="s">
+        <v>678</v>
+      </c>
+      <c r="B341" t="s">
         <v>677</v>
-      </c>
-      <c r="B341" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -10398,15 +10404,15 @@
         <v>717</v>
       </c>
       <c r="B361" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
     </row>
     <row r="362" spans="1:2">
       <c r="A362" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B362" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -10846,15 +10852,15 @@
         <v>828</v>
       </c>
       <c r="B417" t="s">
-        <v>799</v>
+        <v>829</v>
       </c>
     </row>
     <row r="418" spans="1:2">
       <c r="A418" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B418" t="s">
-        <v>830</v>
+        <v>801</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -11262,15 +11268,15 @@
         <v>931</v>
       </c>
       <c r="B469" t="s">
-        <v>638</v>
+        <v>932</v>
       </c>
     </row>
     <row r="470" spans="1:2">
       <c r="A470" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B470" t="s">
-        <v>933</v>
+        <v>640</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -11390,12 +11396,12 @@
         <v>962</v>
       </c>
       <c r="B485" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="486" spans="1:2">
       <c r="A486" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B486" t="s">
         <v>964</v>
@@ -12550,15 +12556,15 @@
         <v>1251</v>
       </c>
       <c r="B630" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="631" spans="1:2">
       <c r="A631" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B631" t="s">
         <v>1252</v>
-      </c>
-      <c r="B631" t="s">
-        <v>1253</v>
       </c>
     </row>
     <row r="632" spans="1:2">
@@ -13982,15 +13988,15 @@
         <v>1608</v>
       </c>
       <c r="B809" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="810" spans="1:2">
       <c r="A810" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B810" t="s">
         <v>1609</v>
-      </c>
-      <c r="B810" t="s">
-        <v>1610</v>
       </c>
     </row>
     <row r="811" spans="1:2">
@@ -14638,12 +14644,12 @@
         <v>1771</v>
       </c>
       <c r="B891" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="B892" t="s">
         <v>1773</v>
@@ -14710,12 +14716,12 @@
         <v>1788</v>
       </c>
       <c r="B900" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="901" spans="1:2">
       <c r="A901" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="B901" t="s">
         <v>1790</v>
@@ -15070,12 +15076,12 @@
         <v>1877</v>
       </c>
       <c r="B945" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="B946" t="s">
         <v>1879</v>
@@ -15686,12 +15692,12 @@
         <v>2030</v>
       </c>
       <c r="B1022" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="B1023" t="s">
         <v>2032</v>
@@ -15966,12 +15972,12 @@
         <v>2099</v>
       </c>
       <c r="B1057" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="B1058" t="s">
         <v>2101</v>
@@ -15998,12 +16004,12 @@
         <v>2106</v>
       </c>
       <c r="B1061" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
-        <v>2107</v>
+        <v>2108</v>
       </c>
       <c r="B1062" t="s">
         <v>2108</v>
@@ -16038,12 +16044,12 @@
         <v>2115</v>
       </c>
       <c r="B1066" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="1067" spans="1:2">
       <c r="A1067" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="B1067" t="s">
         <v>2117</v>
@@ -16166,12 +16172,12 @@
         <v>2146</v>
       </c>
       <c r="B1082" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="B1083" t="s">
         <v>2148</v>
@@ -16334,15 +16340,15 @@
         <v>2187</v>
       </c>
       <c r="B1103" t="s">
-        <v>2186</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
+        <v>2189</v>
+      </c>
+      <c r="B1104" t="s">
         <v>2188</v>
-      </c>
-      <c r="B1104" t="s">
-        <v>2189</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
@@ -16438,12 +16444,12 @@
         <v>2212</v>
       </c>
       <c r="B1116" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>2213</v>
+        <v>2214</v>
       </c>
       <c r="B1117" t="s">
         <v>2214</v>
@@ -16470,12 +16476,12 @@
         <v>2219</v>
       </c>
       <c r="B1120" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>2220</v>
+        <v>2221</v>
       </c>
       <c r="B1121" t="s">
         <v>2221</v>
@@ -16502,12 +16508,12 @@
         <v>2226</v>
       </c>
       <c r="B1124" t="s">
-        <v>2226</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
-        <v>2227</v>
+        <v>2228</v>
       </c>
       <c r="B1125" t="s">
         <v>2228</v>
@@ -16750,12 +16756,12 @@
         <v>2287</v>
       </c>
       <c r="B1155" t="s">
-        <v>2287</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
       <c r="B1156" t="s">
         <v>2289</v>
@@ -17062,15 +17068,15 @@
         <v>2364</v>
       </c>
       <c r="B1194" t="s">
-        <v>920</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="1195" spans="1:2">
       <c r="A1195" t="s">
-        <v>2365</v>
+        <v>2366</v>
       </c>
       <c r="B1195" t="s">
-        <v>2366</v>
+        <v>922</v>
       </c>
     </row>
     <row r="1196" spans="1:2">
@@ -17129,8 +17135,16 @@
         <v>2380</v>
       </c>
     </row>
+    <row r="1203" spans="1:2">
+      <c r="A1203" t="s">
+        <v>2381</v>
+      </c>
+      <c r="B1203" t="s">
+        <v>2382</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1202"/>
+  <autoFilter ref="A1:B1203"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ar/headTags.xlsx
+++ b/lang/ar/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1203</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1204</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2385">
   <si>
     <t>en</t>
   </si>
@@ -2489,6 +2489,12 @@
   </si>
   <si>
     <t>خط (برتقالي)</t>
+  </si>
+  <si>
+    <t>Font (Pale Oak)</t>
+  </si>
+  <si>
+    <t>الخط (Pale Oak)</t>
   </si>
   <si>
     <t>Font (Pink)</t>
@@ -7512,7 +7518,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1203"/>
+  <dimension ref="A1:B1204"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -10860,15 +10866,15 @@
         <v>830</v>
       </c>
       <c r="B418" t="s">
-        <v>801</v>
+        <v>831</v>
       </c>
     </row>
     <row r="419" spans="1:2">
       <c r="A419" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B419" t="s">
-        <v>832</v>
+        <v>801</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -11276,15 +11282,15 @@
         <v>933</v>
       </c>
       <c r="B470" t="s">
-        <v>640</v>
+        <v>934</v>
       </c>
     </row>
     <row r="471" spans="1:2">
       <c r="A471" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B471" t="s">
-        <v>935</v>
+        <v>640</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -11404,12 +11410,12 @@
         <v>964</v>
       </c>
       <c r="B486" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="487" spans="1:2">
       <c r="A487" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B487" t="s">
         <v>966</v>
@@ -12564,15 +12570,15 @@
         <v>1253</v>
       </c>
       <c r="B631" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="632" spans="1:2">
       <c r="A632" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B632" t="s">
         <v>1254</v>
-      </c>
-      <c r="B632" t="s">
-        <v>1255</v>
       </c>
     </row>
     <row r="633" spans="1:2">
@@ -13996,15 +14002,15 @@
         <v>1610</v>
       </c>
       <c r="B810" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="811" spans="1:2">
       <c r="A811" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B811" t="s">
         <v>1611</v>
-      </c>
-      <c r="B811" t="s">
-        <v>1612</v>
       </c>
     </row>
     <row r="812" spans="1:2">
@@ -14652,12 +14658,12 @@
         <v>1773</v>
       </c>
       <c r="B892" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="B893" t="s">
         <v>1775</v>
@@ -14724,12 +14730,12 @@
         <v>1790</v>
       </c>
       <c r="B901" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="B902" t="s">
         <v>1792</v>
@@ -15084,12 +15090,12 @@
         <v>1879</v>
       </c>
       <c r="B946" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="947" spans="1:2">
       <c r="A947" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="B947" t="s">
         <v>1881</v>
@@ -15700,12 +15706,12 @@
         <v>2032</v>
       </c>
       <c r="B1023" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="B1024" t="s">
         <v>2034</v>
@@ -15980,12 +15986,12 @@
         <v>2101</v>
       </c>
       <c r="B1058" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="B1059" t="s">
         <v>2103</v>
@@ -16012,12 +16018,12 @@
         <v>2108</v>
       </c>
       <c r="B1062" t="s">
-        <v>2108</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="B1063" t="s">
         <v>2110</v>
@@ -16052,12 +16058,12 @@
         <v>2117</v>
       </c>
       <c r="B1067" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="B1068" t="s">
         <v>2119</v>
@@ -16180,12 +16186,12 @@
         <v>2148</v>
       </c>
       <c r="B1083" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="B1084" t="s">
         <v>2150</v>
@@ -16348,15 +16354,15 @@
         <v>2189</v>
       </c>
       <c r="B1104" t="s">
-        <v>2188</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
+        <v>2191</v>
+      </c>
+      <c r="B1105" t="s">
         <v>2190</v>
-      </c>
-      <c r="B1105" t="s">
-        <v>2191</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
@@ -16452,12 +16458,12 @@
         <v>2214</v>
       </c>
       <c r="B1117" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
       <c r="B1118" t="s">
         <v>2216</v>
@@ -16484,12 +16490,12 @@
         <v>2221</v>
       </c>
       <c r="B1121" t="s">
-        <v>2221</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>2222</v>
+        <v>2223</v>
       </c>
       <c r="B1122" t="s">
         <v>2223</v>
@@ -16516,12 +16522,12 @@
         <v>2228</v>
       </c>
       <c r="B1125" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
       <c r="B1126" t="s">
         <v>2230</v>
@@ -16764,12 +16770,12 @@
         <v>2289</v>
       </c>
       <c r="B1156" t="s">
-        <v>2289</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>2290</v>
+        <v>2291</v>
       </c>
       <c r="B1157" t="s">
         <v>2291</v>
@@ -17076,15 +17082,15 @@
         <v>2366</v>
       </c>
       <c r="B1195" t="s">
-        <v>922</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="1196" spans="1:2">
       <c r="A1196" t="s">
-        <v>2367</v>
+        <v>2368</v>
       </c>
       <c r="B1196" t="s">
-        <v>2368</v>
+        <v>924</v>
       </c>
     </row>
     <row r="1197" spans="1:2">
@@ -17143,8 +17149,16 @@
         <v>2382</v>
       </c>
     </row>
+    <row r="1204" spans="1:2">
+      <c r="A1204" t="s">
+        <v>2383</v>
+      </c>
+      <c r="B1204" t="s">
+        <v>2384</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1203"/>
+  <autoFilter ref="A1:B1204"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
